--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6708,7 +6708,7 @@
         <v>119823610</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,10 +6817,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121754592</v>
+        <v>121752813</v>
       </c>
       <c r="B53" t="n">
-        <v>91133</v>
+        <v>105218</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6833,37 +6833,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>595015</v>
+        <v>594841</v>
       </c>
       <c r="R53" t="n">
-        <v>6396186</v>
+        <v>6396038</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6895,7 +6901,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6905,7 +6911,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6914,7 +6920,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6926,17 +6931,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121752813</v>
+        <v>121753875</v>
       </c>
       <c r="B54" t="n">
-        <v>105218</v>
+        <v>57726</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6949,46 +6954,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594841</v>
+        <v>594778</v>
       </c>
       <c r="R54" t="n">
-        <v>6396038</v>
+        <v>6396263</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7017,7 +7013,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7027,7 +7023,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7054,10 +7050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121752765</v>
+        <v>121752859</v>
       </c>
       <c r="B55" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7066,30 +7062,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7106,13 +7102,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>594837</v>
+        <v>594807</v>
       </c>
       <c r="R55" t="n">
-        <v>6396023</v>
+        <v>6396047</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7141,7 +7137,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7151,7 +7147,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7179,10 +7175,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121754357</v>
+        <v>121754826</v>
       </c>
       <c r="B56" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7191,41 +7187,53 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594927</v>
+        <v>595008</v>
       </c>
       <c r="R56" t="n">
-        <v>6396335</v>
+        <v>6396135</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7254,7 +7262,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7264,7 +7272,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7273,6 +7281,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7284,14 +7293,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121754826</v>
+        <v>121752765</v>
       </c>
       <c r="B57" t="n">
         <v>98113</v>
@@ -7326,7 +7335,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7339,17 +7348,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595008</v>
+        <v>594837</v>
       </c>
       <c r="R57" t="n">
-        <v>6396135</v>
+        <v>6396023</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7378,7 +7387,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7388,7 +7397,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7528,10 +7537,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121753048</v>
+        <v>121754357</v>
       </c>
       <c r="B59" t="n">
-        <v>57726</v>
+        <v>105218</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7544,41 +7553,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594817</v>
+        <v>594927</v>
       </c>
       <c r="R59" t="n">
-        <v>6396099</v>
+        <v>6396335</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7607,7 +7612,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7617,7 +7622,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7637,14 +7642,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121753875</v>
+        <v>121753048</v>
       </c>
       <c r="B60" t="n">
         <v>57726</v>
@@ -7678,16 +7683,20 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594778</v>
+        <v>594817</v>
       </c>
       <c r="R60" t="n">
-        <v>6396263</v>
+        <v>6396099</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7719,7 +7728,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7729,7 +7738,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7749,17 +7758,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121754718</v>
+        <v>121754592</v>
       </c>
       <c r="B61" t="n">
-        <v>98113</v>
+        <v>91133</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7768,39 +7777,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7808,13 +7808,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594994</v>
+        <v>595015</v>
       </c>
       <c r="R61" t="n">
-        <v>6396168</v>
+        <v>6396186</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7853,12 +7853,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7998,10 +7993,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121752859</v>
+        <v>121754718</v>
       </c>
       <c r="B63" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8010,30 +8005,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8046,17 +8041,17 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594807</v>
+        <v>594994</v>
       </c>
       <c r="R63" t="n">
-        <v>6396047</v>
+        <v>6396168</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8085,7 +8080,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8095,7 +8090,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8123,10 +8123,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121763762</v>
+        <v>121764675</v>
       </c>
       <c r="B64" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8135,42 +8135,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>594945</v>
+        <v>595041</v>
       </c>
       <c r="R64" t="n">
-        <v>6396373</v>
+        <v>6396281</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8202,7 +8198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8212,7 +8208,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8221,7 +8217,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8240,7 +8235,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121765794</v>
+        <v>121766306</v>
       </c>
       <c r="B65" t="n">
         <v>105218</v>
@@ -8280,10 +8275,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594763</v>
+        <v>594815</v>
       </c>
       <c r="R65" t="n">
-        <v>6396128</v>
+        <v>6396038</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8315,7 +8310,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8325,7 +8320,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8352,10 +8347,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121764658</v>
+        <v>121765532</v>
       </c>
       <c r="B66" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8364,43 +8359,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595027</v>
+        <v>594790</v>
       </c>
       <c r="R66" t="n">
-        <v>6396283</v>
+        <v>6396232</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8432,7 +8422,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8442,7 +8432,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8469,10 +8459,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121766306</v>
+        <v>121763762</v>
       </c>
       <c r="B67" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8481,38 +8471,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594815</v>
+        <v>594945</v>
       </c>
       <c r="R67" t="n">
-        <v>6396038</v>
+        <v>6396373</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8544,7 +8538,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8554,7 +8548,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8563,6 +8557,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8581,7 +8576,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121764675</v>
+        <v>121765794</v>
       </c>
       <c r="B68" t="n">
         <v>105218</v>
@@ -8617,14 +8612,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595041</v>
+        <v>594763</v>
       </c>
       <c r="R68" t="n">
-        <v>6396281</v>
+        <v>6396128</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8656,7 +8651,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8666,7 +8661,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8693,10 +8688,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121765532</v>
+        <v>121763950</v>
       </c>
       <c r="B69" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8705,38 +8700,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>594790</v>
+        <v>594958</v>
       </c>
       <c r="R69" t="n">
-        <v>6396232</v>
+        <v>6396369</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8805,7 +8805,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121763950</v>
+        <v>121764658</v>
       </c>
       <c r="B70" t="n">
         <v>57373</v>
@@ -8846,14 +8846,14 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>594958</v>
+        <v>595027</v>
       </c>
       <c r="R70" t="n">
-        <v>6396369</v>
+        <v>6396283</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,7 +6817,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121752813</v>
+        <v>121753035</v>
       </c>
       <c r="B53" t="n">
         <v>105218</v>
@@ -6850,29 +6850,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594841</v>
+        <v>594815</v>
       </c>
       <c r="R53" t="n">
-        <v>6396038</v>
+        <v>6396098</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6901,7 +6892,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6911,7 +6902,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6938,10 +6929,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121753875</v>
+        <v>121754826</v>
       </c>
       <c r="B54" t="n">
-        <v>57726</v>
+        <v>98113</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6950,41 +6941,53 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594778</v>
+        <v>595008</v>
       </c>
       <c r="R54" t="n">
-        <v>6396263</v>
+        <v>6396135</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7013,7 +7016,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7023,7 +7026,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7032,6 +7035,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7043,14 +7047,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121752859</v>
+        <v>121754357</v>
       </c>
       <c r="B55" t="n">
         <v>105218</v>
@@ -7083,32 +7087,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>594807</v>
+        <v>594927</v>
       </c>
       <c r="R55" t="n">
-        <v>6396047</v>
+        <v>6396335</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7137,7 +7129,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7147,7 +7139,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7156,7 +7148,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7168,17 +7159,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121754826</v>
+        <v>121752813</v>
       </c>
       <c r="B56" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7187,30 +7178,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7218,22 +7209,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595008</v>
+        <v>594841</v>
       </c>
       <c r="R56" t="n">
-        <v>6396135</v>
+        <v>6396038</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7262,7 +7250,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7272,7 +7260,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7281,7 +7269,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7293,17 +7280,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121752765</v>
+        <v>121752859</v>
       </c>
       <c r="B57" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7312,30 +7299,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7352,13 +7339,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594837</v>
+        <v>594807</v>
       </c>
       <c r="R57" t="n">
-        <v>6396023</v>
+        <v>6396047</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7387,7 +7374,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7397,7 +7384,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7425,10 +7412,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121752698</v>
+        <v>121752765</v>
       </c>
       <c r="B58" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7437,38 +7424,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594887</v>
+        <v>594837</v>
       </c>
       <c r="R58" t="n">
-        <v>6396036</v>
+        <v>6396023</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7500,7 +7499,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7510,7 +7509,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7519,6 +7518,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7530,17 +7530,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121754357</v>
+        <v>121754592</v>
       </c>
       <c r="B59" t="n">
-        <v>105218</v>
+        <v>91133</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7553,34 +7553,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594927</v>
+        <v>595015</v>
       </c>
       <c r="R59" t="n">
-        <v>6396335</v>
+        <v>6396186</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7612,7 +7615,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7622,7 +7625,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7631,6 +7634,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7642,17 +7646,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121753048</v>
+        <v>121752698</v>
       </c>
       <c r="B60" t="n">
-        <v>57726</v>
+        <v>105218</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7665,41 +7669,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594817</v>
+        <v>594887</v>
       </c>
       <c r="R60" t="n">
-        <v>6396099</v>
+        <v>6396036</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121754592</v>
+        <v>121753048</v>
       </c>
       <c r="B61" t="n">
-        <v>91133</v>
+        <v>57726</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7781,40 +7781,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595015</v>
+        <v>594817</v>
       </c>
       <c r="R61" t="n">
-        <v>6396186</v>
+        <v>6396099</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7843,7 +7844,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7853,7 +7854,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7862,7 +7863,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121753035</v>
+        <v>121753875</v>
       </c>
       <c r="B62" t="n">
-        <v>105218</v>
+        <v>57726</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7897,37 +7897,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>594815</v>
+        <v>594778</v>
       </c>
       <c r="R62" t="n">
-        <v>6396098</v>
+        <v>6396263</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8123,10 +8123,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121764675</v>
+        <v>121763762</v>
       </c>
       <c r="B64" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8135,38 +8135,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595041</v>
+        <v>594945</v>
       </c>
       <c r="R64" t="n">
-        <v>6396281</v>
+        <v>6396373</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8198,7 +8202,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8208,7 +8212,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8217,6 +8221,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8235,7 +8240,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121766306</v>
+        <v>121765794</v>
       </c>
       <c r="B65" t="n">
         <v>105218</v>
@@ -8275,10 +8280,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594815</v>
+        <v>594763</v>
       </c>
       <c r="R65" t="n">
-        <v>6396038</v>
+        <v>6396128</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8310,7 +8315,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8320,7 +8325,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8347,7 +8352,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121765532</v>
+        <v>121764675</v>
       </c>
       <c r="B66" t="n">
         <v>105218</v>
@@ -8387,10 +8392,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>594790</v>
+        <v>595041</v>
       </c>
       <c r="R66" t="n">
-        <v>6396232</v>
+        <v>6396281</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8422,7 +8427,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8432,7 +8437,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8459,10 +8464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121763762</v>
+        <v>121764658</v>
       </c>
       <c r="B67" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8471,42 +8476,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594945</v>
+        <v>595027</v>
       </c>
       <c r="R67" t="n">
-        <v>6396373</v>
+        <v>6396283</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8538,7 +8544,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8548,7 +8554,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8557,7 +8563,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8576,10 +8581,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121765794</v>
+        <v>121763950</v>
       </c>
       <c r="B68" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8588,38 +8593,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>594763</v>
+        <v>594958</v>
       </c>
       <c r="R68" t="n">
-        <v>6396128</v>
+        <v>6396369</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8651,7 +8661,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8661,7 +8671,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8688,10 +8698,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121763950</v>
+        <v>121766306</v>
       </c>
       <c r="B69" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8700,43 +8710,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>594958</v>
+        <v>594815</v>
       </c>
       <c r="R69" t="n">
-        <v>6396369</v>
+        <v>6396038</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8768,7 +8773,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8778,7 +8783,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8805,10 +8810,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121764658</v>
+        <v>121765532</v>
       </c>
       <c r="B70" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8817,43 +8822,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595027</v>
+        <v>594790</v>
       </c>
       <c r="R70" t="n">
-        <v>6396283</v>
+        <v>6396232</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,10 +6817,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121753035</v>
+        <v>121754718</v>
       </c>
       <c r="B53" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6829,41 +6829,53 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594815</v>
+        <v>594994</v>
       </c>
       <c r="R53" t="n">
-        <v>6396098</v>
+        <v>6396168</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6892,7 +6904,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6902,7 +6914,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6911,6 +6928,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6922,7 +6940,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7054,10 +7072,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121754357</v>
+        <v>121754592</v>
       </c>
       <c r="B55" t="n">
-        <v>105218</v>
+        <v>91133</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7070,34 +7088,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>594927</v>
+        <v>595015</v>
       </c>
       <c r="R55" t="n">
-        <v>6396335</v>
+        <v>6396186</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7129,7 +7150,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7139,7 +7160,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7148,6 +7169,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7159,14 +7181,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121752813</v>
+        <v>121753035</v>
       </c>
       <c r="B56" t="n">
         <v>105218</v>
@@ -7199,29 +7221,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594841</v>
+        <v>594815</v>
       </c>
       <c r="R56" t="n">
-        <v>6396038</v>
+        <v>6396098</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7250,7 +7263,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7260,7 +7273,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7287,10 +7300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121752859</v>
+        <v>121753048</v>
       </c>
       <c r="B57" t="n">
-        <v>105218</v>
+        <v>57726</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7303,35 +7316,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7339,13 +7344,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594807</v>
+        <v>594817</v>
       </c>
       <c r="R57" t="n">
-        <v>6396047</v>
+        <v>6396099</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7374,7 +7379,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7384,7 +7389,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7393,7 +7398,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7412,10 +7416,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121752765</v>
+        <v>121754357</v>
       </c>
       <c r="B58" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7424,50 +7428,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594837</v>
+        <v>594927</v>
       </c>
       <c r="R58" t="n">
-        <v>6396023</v>
+        <v>6396335</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7499,7 +7491,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7509,7 +7501,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7518,7 +7510,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7530,17 +7521,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121754592</v>
+        <v>121752859</v>
       </c>
       <c r="B59" t="n">
-        <v>91133</v>
+        <v>105218</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7553,40 +7544,49 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595015</v>
+        <v>594807</v>
       </c>
       <c r="R59" t="n">
-        <v>6396186</v>
+        <v>6396047</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7653,10 +7653,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121752698</v>
+        <v>121752765</v>
       </c>
       <c r="B60" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7665,38 +7665,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594887</v>
+        <v>594837</v>
       </c>
       <c r="R60" t="n">
-        <v>6396036</v>
+        <v>6396023</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7728,7 +7740,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7738,7 +7750,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7747,6 +7759,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7758,17 +7771,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121753048</v>
+        <v>121752698</v>
       </c>
       <c r="B61" t="n">
-        <v>57726</v>
+        <v>105218</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7781,41 +7794,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594817</v>
+        <v>594887</v>
       </c>
       <c r="R61" t="n">
-        <v>6396099</v>
+        <v>6396036</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7844,7 +7853,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7854,7 +7863,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7874,17 +7883,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121753875</v>
+        <v>121752813</v>
       </c>
       <c r="B62" t="n">
-        <v>57726</v>
+        <v>105218</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7897,37 +7906,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>594778</v>
+        <v>594841</v>
       </c>
       <c r="R62" t="n">
-        <v>6396263</v>
+        <v>6396038</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7956,7 +7974,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7966,7 +7984,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7993,10 +8011,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121754718</v>
+        <v>121753875</v>
       </c>
       <c r="B63" t="n">
-        <v>98113</v>
+        <v>57726</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8005,50 +8023,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594994</v>
+        <v>594778</v>
       </c>
       <c r="R63" t="n">
-        <v>6396168</v>
+        <v>6396263</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8080,7 +8086,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8090,12 +8096,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8104,7 +8105,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8240,7 +8240,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121765794</v>
+        <v>121765532</v>
       </c>
       <c r="B65" t="n">
         <v>105218</v>
@@ -8276,14 +8276,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594763</v>
+        <v>594790</v>
       </c>
       <c r="R65" t="n">
-        <v>6396128</v>
+        <v>6396232</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8352,10 +8352,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121764675</v>
+        <v>121764658</v>
       </c>
       <c r="B66" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8364,38 +8364,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595041</v>
+        <v>595027</v>
       </c>
       <c r="R66" t="n">
-        <v>6396281</v>
+        <v>6396283</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8464,10 +8469,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121764658</v>
+        <v>121764675</v>
       </c>
       <c r="B67" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8476,43 +8481,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595027</v>
+        <v>595041</v>
       </c>
       <c r="R67" t="n">
-        <v>6396283</v>
+        <v>6396281</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8698,7 +8698,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121766306</v>
+        <v>121765794</v>
       </c>
       <c r="B69" t="n">
         <v>105218</v>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>594815</v>
+        <v>594763</v>
       </c>
       <c r="R69" t="n">
-        <v>6396038</v>
+        <v>6396128</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8810,7 +8810,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121765532</v>
+        <v>121766306</v>
       </c>
       <c r="B70" t="n">
         <v>105218</v>
@@ -8846,14 +8846,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>594790</v>
+        <v>594815</v>
       </c>
       <c r="R70" t="n">
-        <v>6396232</v>
+        <v>6396038</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,10 +6817,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121754718</v>
+        <v>121753035</v>
       </c>
       <c r="B53" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6829,53 +6829,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594994</v>
+        <v>594815</v>
       </c>
       <c r="R53" t="n">
-        <v>6396168</v>
+        <v>6396098</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6904,7 +6892,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6914,12 +6902,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6928,7 +6911,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6940,17 +6922,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121754826</v>
+        <v>121752813</v>
       </c>
       <c r="B54" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6959,30 +6941,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6990,22 +6972,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>595008</v>
+        <v>594841</v>
       </c>
       <c r="R54" t="n">
-        <v>6396135</v>
+        <v>6396038</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7034,7 +7013,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7044,7 +7023,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7053,7 +7032,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7065,7 +7043,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7188,7 +7166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121753035</v>
+        <v>121752859</v>
       </c>
       <c r="B56" t="n">
         <v>105218</v>
@@ -7221,20 +7199,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594815</v>
+        <v>594807</v>
       </c>
       <c r="R56" t="n">
-        <v>6396098</v>
+        <v>6396047</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7263,7 +7253,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7273,7 +7263,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7282,6 +7272,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7293,14 +7284,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121753048</v>
+        <v>121753875</v>
       </c>
       <c r="B57" t="n">
         <v>57726</v>
@@ -7334,20 +7325,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594817</v>
+        <v>594778</v>
       </c>
       <c r="R57" t="n">
-        <v>6396099</v>
+        <v>6396263</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7379,7 +7366,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7389,7 +7376,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7409,17 +7396,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121754357</v>
+        <v>121753048</v>
       </c>
       <c r="B58" t="n">
-        <v>105218</v>
+        <v>57726</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7432,37 +7419,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594927</v>
+        <v>594817</v>
       </c>
       <c r="R58" t="n">
-        <v>6396335</v>
+        <v>6396099</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7491,7 +7482,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7501,7 +7492,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7521,14 +7512,14 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121752859</v>
+        <v>121754357</v>
       </c>
       <c r="B59" t="n">
         <v>105218</v>
@@ -7561,32 +7552,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594807</v>
+        <v>594927</v>
       </c>
       <c r="R59" t="n">
-        <v>6396047</v>
+        <v>6396335</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7615,7 +7594,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7625,7 +7604,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7634,7 +7613,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7646,17 +7624,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121752765</v>
+        <v>121752698</v>
       </c>
       <c r="B60" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7665,50 +7643,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594837</v>
+        <v>594887</v>
       </c>
       <c r="R60" t="n">
-        <v>6396023</v>
+        <v>6396036</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7740,7 +7706,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7750,7 +7716,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7759,7 +7725,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7771,17 +7736,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121752698</v>
+        <v>121752765</v>
       </c>
       <c r="B61" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7790,38 +7755,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594887</v>
+        <v>594837</v>
       </c>
       <c r="R61" t="n">
-        <v>6396036</v>
+        <v>6396023</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7853,7 +7830,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7863,7 +7840,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7872,6 +7849,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7883,17 +7861,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121752813</v>
+        <v>121754826</v>
       </c>
       <c r="B62" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7902,30 +7880,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7933,19 +7911,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>594841</v>
+        <v>595008</v>
       </c>
       <c r="R62" t="n">
-        <v>6396038</v>
+        <v>6396135</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7974,7 +7955,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7984,7 +7965,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7993,6 +7974,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8004,17 +7986,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121753875</v>
+        <v>121754718</v>
       </c>
       <c r="B63" t="n">
-        <v>57726</v>
+        <v>98113</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8023,38 +8005,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594778</v>
+        <v>594994</v>
       </c>
       <c r="R63" t="n">
-        <v>6396263</v>
+        <v>6396168</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8086,7 +8080,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8096,7 +8090,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8105,6 +8104,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8116,17 +8116,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121763762</v>
+        <v>121765532</v>
       </c>
       <c r="B64" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8135,42 +8135,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>594945</v>
+        <v>594790</v>
       </c>
       <c r="R64" t="n">
-        <v>6396373</v>
+        <v>6396232</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8202,7 +8198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8212,7 +8208,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8221,7 +8217,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8240,7 +8235,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121765532</v>
+        <v>121765794</v>
       </c>
       <c r="B65" t="n">
         <v>105218</v>
@@ -8276,14 +8271,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594790</v>
+        <v>594763</v>
       </c>
       <c r="R65" t="n">
-        <v>6396232</v>
+        <v>6396128</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8315,7 +8310,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8325,7 +8320,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8352,10 +8347,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121764658</v>
+        <v>121766306</v>
       </c>
       <c r="B66" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8364,43 +8359,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595027</v>
+        <v>594815</v>
       </c>
       <c r="R66" t="n">
-        <v>6396283</v>
+        <v>6396038</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8432,7 +8422,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8442,7 +8432,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8469,10 +8459,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121764675</v>
+        <v>121763762</v>
       </c>
       <c r="B67" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8481,38 +8471,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>595041</v>
+        <v>594945</v>
       </c>
       <c r="R67" t="n">
-        <v>6396281</v>
+        <v>6396373</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8544,7 +8538,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8554,7 +8548,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8563,6 +8557,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8698,7 +8693,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121765794</v>
+        <v>121764675</v>
       </c>
       <c r="B69" t="n">
         <v>105218</v>
@@ -8734,14 +8729,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>594763</v>
+        <v>595041</v>
       </c>
       <c r="R69" t="n">
-        <v>6396128</v>
+        <v>6396281</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8773,7 +8768,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8783,7 +8778,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8810,10 +8805,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121766306</v>
+        <v>121764658</v>
       </c>
       <c r="B70" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8822,38 +8817,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>594815</v>
+        <v>595027</v>
       </c>
       <c r="R70" t="n">
-        <v>6396038</v>
+        <v>6396283</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,7 +6817,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121753035</v>
+        <v>121752859</v>
       </c>
       <c r="B53" t="n">
         <v>105218</v>
@@ -6850,20 +6850,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594815</v>
+        <v>594807</v>
       </c>
       <c r="R53" t="n">
-        <v>6396098</v>
+        <v>6396047</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6892,7 +6904,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6902,7 +6914,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6911,6 +6923,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6922,7 +6935,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7050,10 +7063,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121754592</v>
+        <v>121754826</v>
       </c>
       <c r="B55" t="n">
-        <v>91133</v>
+        <v>98113</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7062,30 +7075,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7093,13 +7115,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595015</v>
+        <v>595008</v>
       </c>
       <c r="R55" t="n">
-        <v>6396186</v>
+        <v>6396135</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7128,7 +7150,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7138,7 +7160,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7166,7 +7188,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121752859</v>
+        <v>121753035</v>
       </c>
       <c r="B56" t="n">
         <v>105218</v>
@@ -7199,32 +7221,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594807</v>
+        <v>594815</v>
       </c>
       <c r="R56" t="n">
-        <v>6396047</v>
+        <v>6396098</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7253,7 +7263,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7263,7 +7273,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7272,7 +7282,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7284,14 +7293,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121753875</v>
+        <v>121753048</v>
       </c>
       <c r="B57" t="n">
         <v>57726</v>
@@ -7325,16 +7334,20 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594778</v>
+        <v>594817</v>
       </c>
       <c r="R57" t="n">
-        <v>6396263</v>
+        <v>6396099</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7366,7 +7379,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7376,7 +7389,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7396,17 +7409,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121753048</v>
+        <v>121754592</v>
       </c>
       <c r="B58" t="n">
-        <v>57726</v>
+        <v>91133</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7419,41 +7432,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594817</v>
+        <v>595015</v>
       </c>
       <c r="R58" t="n">
-        <v>6396099</v>
+        <v>6396186</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7482,7 +7494,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7492,7 +7504,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7501,6 +7513,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7519,10 +7532,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121754357</v>
+        <v>121753875</v>
       </c>
       <c r="B59" t="n">
-        <v>105218</v>
+        <v>57726</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7535,37 +7548,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594927</v>
+        <v>594778</v>
       </c>
       <c r="R59" t="n">
-        <v>6396335</v>
+        <v>6396263</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7594,7 +7607,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7604,7 +7617,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7631,10 +7644,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121752698</v>
+        <v>121754718</v>
       </c>
       <c r="B60" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7643,41 +7656,53 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594887</v>
+        <v>594994</v>
       </c>
       <c r="R60" t="n">
-        <v>6396036</v>
+        <v>6396168</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7706,7 +7731,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7716,7 +7741,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7725,6 +7755,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7736,17 +7767,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121752765</v>
+        <v>121754357</v>
       </c>
       <c r="B61" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7755,50 +7786,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594837</v>
+        <v>594927</v>
       </c>
       <c r="R61" t="n">
-        <v>6396023</v>
+        <v>6396335</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7830,7 +7849,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7840,7 +7859,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7849,7 +7868,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7861,14 +7879,14 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121754826</v>
+        <v>121752765</v>
       </c>
       <c r="B62" t="n">
         <v>98113</v>
@@ -7903,7 +7921,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7916,17 +7934,17 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595008</v>
+        <v>594837</v>
       </c>
       <c r="R62" t="n">
-        <v>6396135</v>
+        <v>6396023</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7955,7 +7973,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7965,7 +7983,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7993,10 +8011,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121754718</v>
+        <v>121752698</v>
       </c>
       <c r="B63" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8005,53 +8023,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594994</v>
+        <v>594887</v>
       </c>
       <c r="R63" t="n">
-        <v>6396168</v>
+        <v>6396036</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8080,7 +8086,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8090,12 +8096,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8104,7 +8105,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8116,14 +8116,14 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121765532</v>
+        <v>121764675</v>
       </c>
       <c r="B64" t="n">
         <v>105218</v>
@@ -8163,10 +8163,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>594790</v>
+        <v>595041</v>
       </c>
       <c r="R64" t="n">
-        <v>6396232</v>
+        <v>6396281</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8347,7 +8347,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121766306</v>
+        <v>121765532</v>
       </c>
       <c r="B66" t="n">
         <v>105218</v>
@@ -8383,14 +8383,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>594815</v>
+        <v>594790</v>
       </c>
       <c r="R66" t="n">
-        <v>6396038</v>
+        <v>6396232</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8459,10 +8459,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121763762</v>
+        <v>121763950</v>
       </c>
       <c r="B67" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8471,42 +8471,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594945</v>
+        <v>594958</v>
       </c>
       <c r="R67" t="n">
-        <v>6396373</v>
+        <v>6396369</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8538,7 +8539,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8548,7 +8549,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8557,7 +8558,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8576,10 +8576,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121763950</v>
+        <v>121766306</v>
       </c>
       <c r="B68" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8588,43 +8588,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>594958</v>
+        <v>594815</v>
       </c>
       <c r="R68" t="n">
-        <v>6396369</v>
+        <v>6396038</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8656,7 +8651,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8666,7 +8661,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8693,10 +8688,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121764675</v>
+        <v>121764658</v>
       </c>
       <c r="B69" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8705,38 +8700,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595041</v>
+        <v>595027</v>
       </c>
       <c r="R69" t="n">
-        <v>6396281</v>
+        <v>6396283</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8805,10 +8805,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121764658</v>
+        <v>121763762</v>
       </c>
       <c r="B70" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8817,43 +8817,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>595027</v>
+        <v>594945</v>
       </c>
       <c r="R70" t="n">
-        <v>6396283</v>
+        <v>6396373</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8884,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8894,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8904,6 +8903,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,7 +6817,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121752859</v>
+        <v>121754357</v>
       </c>
       <c r="B53" t="n">
         <v>105218</v>
@@ -6850,32 +6850,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594807</v>
+        <v>594927</v>
       </c>
       <c r="R53" t="n">
-        <v>6396047</v>
+        <v>6396335</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6904,7 +6892,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6914,7 +6902,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6923,7 +6911,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6935,7 +6922,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7188,7 +7175,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121753035</v>
+        <v>121752859</v>
       </c>
       <c r="B56" t="n">
         <v>105218</v>
@@ -7221,20 +7208,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594815</v>
+        <v>594807</v>
       </c>
       <c r="R56" t="n">
-        <v>6396098</v>
+        <v>6396047</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7263,7 +7262,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7273,7 +7272,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7282,6 +7281,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121753048</v>
+        <v>121753035</v>
       </c>
       <c r="B57" t="n">
-        <v>57726</v>
+        <v>105218</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7316,41 +7316,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594817</v>
+        <v>594815</v>
       </c>
       <c r="R57" t="n">
-        <v>6396099</v>
+        <v>6396098</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7379,7 +7375,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7389,7 +7385,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7409,17 +7405,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121754592</v>
+        <v>121754718</v>
       </c>
       <c r="B58" t="n">
-        <v>91133</v>
+        <v>98113</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7428,30 +7424,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7459,13 +7464,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595015</v>
+        <v>594994</v>
       </c>
       <c r="R58" t="n">
-        <v>6396186</v>
+        <v>6396168</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7494,7 +7499,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7504,7 +7509,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7532,10 +7542,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121753875</v>
+        <v>121752765</v>
       </c>
       <c r="B59" t="n">
-        <v>57726</v>
+        <v>98113</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7544,41 +7554,53 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594778</v>
+        <v>594837</v>
       </c>
       <c r="R59" t="n">
-        <v>6396263</v>
+        <v>6396023</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7607,7 +7629,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7617,7 +7639,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7626,6 +7648,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7637,17 +7660,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121754718</v>
+        <v>121753875</v>
       </c>
       <c r="B60" t="n">
-        <v>98113</v>
+        <v>57726</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7656,50 +7679,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594994</v>
+        <v>594778</v>
       </c>
       <c r="R60" t="n">
-        <v>6396168</v>
+        <v>6396263</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7731,7 +7742,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7741,12 +7752,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7755,7 +7761,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7767,14 +7772,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121754357</v>
+        <v>121752698</v>
       </c>
       <c r="B61" t="n">
         <v>105218</v>
@@ -7810,14 +7815,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594927</v>
+        <v>594887</v>
       </c>
       <c r="R61" t="n">
-        <v>6396335</v>
+        <v>6396036</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7849,7 +7854,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7859,7 +7864,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7886,10 +7891,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121752765</v>
+        <v>121754592</v>
       </c>
       <c r="B62" t="n">
-        <v>98113</v>
+        <v>91133</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7898,50 +7903,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>594837</v>
+        <v>595015</v>
       </c>
       <c r="R62" t="n">
-        <v>6396023</v>
+        <v>6396186</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7973,7 +7969,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7983,7 +7979,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8011,10 +8007,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121752698</v>
+        <v>121753048</v>
       </c>
       <c r="B63" t="n">
-        <v>105218</v>
+        <v>57726</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8027,37 +8023,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594887</v>
+        <v>594817</v>
       </c>
       <c r="R63" t="n">
-        <v>6396036</v>
+        <v>6396099</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8116,14 +8116,14 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121764675</v>
+        <v>121766306</v>
       </c>
       <c r="B64" t="n">
         <v>105218</v>
@@ -8159,14 +8159,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>595041</v>
+        <v>594815</v>
       </c>
       <c r="R64" t="n">
-        <v>6396281</v>
+        <v>6396038</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8235,10 +8235,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121765794</v>
+        <v>121763762</v>
       </c>
       <c r="B65" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8247,38 +8247,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594763</v>
+        <v>594945</v>
       </c>
       <c r="R65" t="n">
-        <v>6396128</v>
+        <v>6396373</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8310,7 +8314,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8320,7 +8324,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8329,6 +8333,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8347,7 +8352,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121765532</v>
+        <v>121764675</v>
       </c>
       <c r="B66" t="n">
         <v>105218</v>
@@ -8387,10 +8392,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>594790</v>
+        <v>595041</v>
       </c>
       <c r="R66" t="n">
-        <v>6396232</v>
+        <v>6396281</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8422,7 +8427,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8432,7 +8437,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8459,10 +8464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121763950</v>
+        <v>121765532</v>
       </c>
       <c r="B67" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8471,43 +8476,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594958</v>
+        <v>594790</v>
       </c>
       <c r="R67" t="n">
-        <v>6396369</v>
+        <v>6396232</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8576,10 +8576,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121766306</v>
+        <v>121763950</v>
       </c>
       <c r="B68" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8588,38 +8588,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>594815</v>
+        <v>594958</v>
       </c>
       <c r="R68" t="n">
-        <v>6396038</v>
+        <v>6396369</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8651,7 +8656,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8661,7 +8666,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8805,10 +8810,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121763762</v>
+        <v>121765794</v>
       </c>
       <c r="B70" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8817,42 +8822,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>594945</v>
+        <v>594763</v>
       </c>
       <c r="R70" t="n">
-        <v>6396373</v>
+        <v>6396128</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8884,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8894,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8903,7 +8904,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,10 +6817,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121754357</v>
+        <v>121753035</v>
       </c>
       <c r="B53" t="n">
-        <v>105218</v>
+        <v>105236</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6853,17 +6853,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594927</v>
+        <v>594815</v>
       </c>
       <c r="R53" t="n">
-        <v>6396335</v>
+        <v>6396098</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6929,10 +6929,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121752813</v>
+        <v>121754718</v>
       </c>
       <c r="B54" t="n">
-        <v>105218</v>
+        <v>98131</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6941,30 +6941,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6972,19 +6972,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594841</v>
+        <v>594994</v>
       </c>
       <c r="R54" t="n">
-        <v>6396038</v>
+        <v>6396168</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7013,7 +7016,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7023,7 +7026,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7032,6 +7040,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7043,17 +7052,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121754826</v>
+        <v>121753875</v>
       </c>
       <c r="B55" t="n">
-        <v>98113</v>
+        <v>57734</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7062,53 +7071,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595008</v>
+        <v>594778</v>
       </c>
       <c r="R55" t="n">
-        <v>6396135</v>
+        <v>6396263</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7137,7 +7134,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7147,7 +7144,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7156,7 +7153,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7168,17 +7164,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121752859</v>
+        <v>121754592</v>
       </c>
       <c r="B56" t="n">
-        <v>105218</v>
+        <v>91147</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7191,49 +7187,40 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594807</v>
+        <v>595015</v>
       </c>
       <c r="R56" t="n">
-        <v>6396047</v>
+        <v>6396186</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7262,7 +7249,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7272,7 +7259,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7300,10 +7287,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121753035</v>
+        <v>121753048</v>
       </c>
       <c r="B57" t="n">
-        <v>105218</v>
+        <v>57734</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7316,37 +7303,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594815</v>
+        <v>594817</v>
       </c>
       <c r="R57" t="n">
-        <v>6396098</v>
+        <v>6396099</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7375,7 +7366,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7385,7 +7376,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7405,17 +7396,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121754718</v>
+        <v>121754826</v>
       </c>
       <c r="B58" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7447,7 +7438,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7464,13 +7455,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594994</v>
+        <v>595008</v>
       </c>
       <c r="R58" t="n">
-        <v>6396168</v>
+        <v>6396135</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7499,7 +7490,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7509,12 +7500,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7542,10 +7528,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121752765</v>
+        <v>121752859</v>
       </c>
       <c r="B59" t="n">
-        <v>98113</v>
+        <v>105236</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7554,30 +7540,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7594,13 +7580,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594837</v>
+        <v>594807</v>
       </c>
       <c r="R59" t="n">
-        <v>6396023</v>
+        <v>6396047</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7629,7 +7615,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7639,7 +7625,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7667,10 +7653,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121753875</v>
+        <v>121752698</v>
       </c>
       <c r="B60" t="n">
-        <v>57726</v>
+        <v>105236</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7683,21 +7669,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7707,13 +7693,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594778</v>
+        <v>594887</v>
       </c>
       <c r="R60" t="n">
-        <v>6396263</v>
+        <v>6396036</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7742,7 +7728,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7752,7 +7738,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7779,10 +7765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121752698</v>
+        <v>121754357</v>
       </c>
       <c r="B61" t="n">
-        <v>105218</v>
+        <v>105236</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7815,14 +7801,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594887</v>
+        <v>594927</v>
       </c>
       <c r="R61" t="n">
-        <v>6396036</v>
+        <v>6396335</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7854,7 +7840,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7864,7 +7850,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7891,10 +7877,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121754592</v>
+        <v>121752765</v>
       </c>
       <c r="B62" t="n">
-        <v>91133</v>
+        <v>98131</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7903,41 +7889,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595015</v>
+        <v>594837</v>
       </c>
       <c r="R62" t="n">
-        <v>6396186</v>
+        <v>6396023</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7969,7 +7964,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7979,7 +7974,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8007,10 +8002,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121753048</v>
+        <v>121752813</v>
       </c>
       <c r="B63" t="n">
-        <v>57726</v>
+        <v>105236</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8023,41 +8018,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594817</v>
+        <v>594841</v>
       </c>
       <c r="R63" t="n">
-        <v>6396099</v>
+        <v>6396038</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8116,17 +8116,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121766306</v>
+        <v>121763762</v>
       </c>
       <c r="B64" t="n">
-        <v>105218</v>
+        <v>98131</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8135,38 +8135,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>594815</v>
+        <v>594945</v>
       </c>
       <c r="R64" t="n">
-        <v>6396038</v>
+        <v>6396373</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8198,7 +8202,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8208,7 +8212,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8217,6 +8221,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8235,10 +8240,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121763762</v>
+        <v>121764658</v>
       </c>
       <c r="B65" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8247,42 +8252,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594945</v>
+        <v>595027</v>
       </c>
       <c r="R65" t="n">
-        <v>6396373</v>
+        <v>6396283</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8314,7 +8320,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8324,7 +8330,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8333,7 +8339,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8352,10 +8357,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121764675</v>
+        <v>121765532</v>
       </c>
       <c r="B66" t="n">
-        <v>105218</v>
+        <v>105236</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8392,10 +8397,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595041</v>
+        <v>594790</v>
       </c>
       <c r="R66" t="n">
-        <v>6396281</v>
+        <v>6396232</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8427,7 +8432,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8437,7 +8442,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8464,10 +8469,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121765532</v>
+        <v>121765794</v>
       </c>
       <c r="B67" t="n">
-        <v>105218</v>
+        <v>105236</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8500,14 +8505,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594790</v>
+        <v>594763</v>
       </c>
       <c r="R67" t="n">
-        <v>6396232</v>
+        <v>6396128</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8539,7 +8544,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8549,7 +8554,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8576,10 +8581,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121763950</v>
+        <v>121764675</v>
       </c>
       <c r="B68" t="n">
-        <v>57373</v>
+        <v>105236</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8588,43 +8593,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>594958</v>
+        <v>595041</v>
       </c>
       <c r="R68" t="n">
-        <v>6396369</v>
+        <v>6396281</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8693,10 +8693,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121764658</v>
+        <v>121763950</v>
       </c>
       <c r="B69" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8734,14 +8734,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>595027</v>
+        <v>594958</v>
       </c>
       <c r="R69" t="n">
-        <v>6396283</v>
+        <v>6396369</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121765794</v>
+        <v>121766306</v>
       </c>
       <c r="B70" t="n">
-        <v>105218</v>
+        <v>105236</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>594763</v>
+        <v>594815</v>
       </c>
       <c r="R70" t="n">
-        <v>6396128</v>
+        <v>6396038</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -6817,10 +6817,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121753035</v>
+        <v>121754826</v>
       </c>
       <c r="B53" t="n">
-        <v>105236</v>
+        <v>98133</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6829,38 +6829,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594815</v>
+        <v>595008</v>
       </c>
       <c r="R53" t="n">
-        <v>6396098</v>
+        <v>6396135</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6892,7 +6904,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6902,7 +6914,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6911,6 +6923,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6922,7 +6935,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6932,7 +6945,7 @@
         <v>121754718</v>
       </c>
       <c r="B54" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7059,10 +7072,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121753875</v>
+        <v>121754592</v>
       </c>
       <c r="B55" t="n">
-        <v>57734</v>
+        <v>91149</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7075,37 +7088,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>594778</v>
+        <v>595015</v>
       </c>
       <c r="R55" t="n">
-        <v>6396263</v>
+        <v>6396186</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7134,7 +7150,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7144,7 +7160,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7153,6 +7169,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7164,17 +7181,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121754592</v>
+        <v>121752698</v>
       </c>
       <c r="B56" t="n">
-        <v>91147</v>
+        <v>105238</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7187,37 +7204,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595015</v>
+        <v>594887</v>
       </c>
       <c r="R56" t="n">
-        <v>6396186</v>
+        <v>6396036</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7249,7 +7263,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7259,7 +7273,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7268,7 +7282,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7280,14 +7293,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121753048</v>
+        <v>121753875</v>
       </c>
       <c r="B57" t="n">
         <v>57734</v>
@@ -7321,20 +7334,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594817</v>
+        <v>594778</v>
       </c>
       <c r="R57" t="n">
-        <v>6396099</v>
+        <v>6396263</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7366,7 +7375,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7376,7 +7385,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7396,17 +7405,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121754826</v>
+        <v>121752813</v>
       </c>
       <c r="B58" t="n">
-        <v>98131</v>
+        <v>105238</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7415,30 +7424,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7446,22 +7455,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595008</v>
+        <v>594841</v>
       </c>
       <c r="R58" t="n">
-        <v>6396135</v>
+        <v>6396038</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7490,7 +7496,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7500,7 +7506,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7509,7 +7515,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7521,17 +7526,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121752859</v>
+        <v>121754357</v>
       </c>
       <c r="B59" t="n">
-        <v>105236</v>
+        <v>105238</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7561,32 +7566,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594807</v>
+        <v>594927</v>
       </c>
       <c r="R59" t="n">
-        <v>6396047</v>
+        <v>6396335</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7615,7 +7608,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7625,7 +7618,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7634,7 +7627,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7646,17 +7638,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121752698</v>
+        <v>121752765</v>
       </c>
       <c r="B60" t="n">
-        <v>105236</v>
+        <v>98133</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7665,38 +7657,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594887</v>
+        <v>594837</v>
       </c>
       <c r="R60" t="n">
-        <v>6396036</v>
+        <v>6396023</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7728,7 +7732,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7738,7 +7742,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7747,6 +7751,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7758,17 +7763,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121754357</v>
+        <v>121753048</v>
       </c>
       <c r="B61" t="n">
-        <v>105236</v>
+        <v>57734</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7781,37 +7786,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594927</v>
+        <v>594817</v>
       </c>
       <c r="R61" t="n">
-        <v>6396335</v>
+        <v>6396099</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7840,7 +7849,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7850,7 +7859,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7870,17 +7879,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121752765</v>
+        <v>121752859</v>
       </c>
       <c r="B62" t="n">
-        <v>98131</v>
+        <v>105238</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7889,30 +7898,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7929,13 +7938,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>594837</v>
+        <v>594807</v>
       </c>
       <c r="R62" t="n">
-        <v>6396023</v>
+        <v>6396047</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7964,7 +7973,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7974,7 +7983,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8002,10 +8011,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121752813</v>
+        <v>121753035</v>
       </c>
       <c r="B63" t="n">
-        <v>105236</v>
+        <v>105238</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8035,29 +8044,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594841</v>
+        <v>594815</v>
       </c>
       <c r="R63" t="n">
-        <v>6396038</v>
+        <v>6396098</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8123,10 +8123,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121763762</v>
+        <v>121765532</v>
       </c>
       <c r="B64" t="n">
-        <v>98131</v>
+        <v>105238</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8135,42 +8135,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>594945</v>
+        <v>594790</v>
       </c>
       <c r="R64" t="n">
-        <v>6396373</v>
+        <v>6396232</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -8202,7 +8198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8212,7 +8208,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8221,7 +8217,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8240,10 +8235,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121764658</v>
+        <v>121763762</v>
       </c>
       <c r="B65" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8252,43 +8247,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>595027</v>
+        <v>594945</v>
       </c>
       <c r="R65" t="n">
-        <v>6396283</v>
+        <v>6396373</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -8320,7 +8314,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8330,7 +8324,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8339,6 +8333,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8357,10 +8352,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121765532</v>
+        <v>121763950</v>
       </c>
       <c r="B66" t="n">
-        <v>105236</v>
+        <v>57381</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8369,38 +8364,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>594790</v>
+        <v>594958</v>
       </c>
       <c r="R66" t="n">
-        <v>6396232</v>
+        <v>6396369</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8469,10 +8469,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121765794</v>
+        <v>121764658</v>
       </c>
       <c r="B67" t="n">
-        <v>105236</v>
+        <v>57381</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8481,38 +8481,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594763</v>
+        <v>595027</v>
       </c>
       <c r="R67" t="n">
-        <v>6396128</v>
+        <v>6396283</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8544,7 +8549,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8554,7 +8559,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8581,10 +8586,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121764675</v>
+        <v>121766306</v>
       </c>
       <c r="B68" t="n">
-        <v>105236</v>
+        <v>105238</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8617,14 +8622,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595041</v>
+        <v>594815</v>
       </c>
       <c r="R68" t="n">
-        <v>6396281</v>
+        <v>6396038</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8656,7 +8661,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8666,7 +8671,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8693,10 +8698,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121763950</v>
+        <v>121764675</v>
       </c>
       <c r="B69" t="n">
-        <v>57381</v>
+        <v>105238</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8705,43 +8710,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>594958</v>
+        <v>595041</v>
       </c>
       <c r="R69" t="n">
-        <v>6396369</v>
+        <v>6396281</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121766306</v>
+        <v>121765794</v>
       </c>
       <c r="B70" t="n">
-        <v>105236</v>
+        <v>105238</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>594815</v>
+        <v>594763</v>
       </c>
       <c r="R70" t="n">
-        <v>6396038</v>
+        <v>6396128</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 30779-2023 artfynd.xlsx
+++ b/artfynd/A 30779-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110635067</v>
+        <v>112236387</v>
       </c>
       <c r="B2" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1619</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,19 +714,20 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595125.8014220446</v>
+        <v>594893</v>
       </c>
       <c r="R2" t="n">
-        <v>6396072.244815239</v>
+        <v>6396172</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lågt på asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,72 +780,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110637139</v>
+        <v>112237682</v>
       </c>
       <c r="B3" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dagsbo (Dagsbo), Sm</t>
+          <t>Storön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594774.1513157194</v>
+        <v>595194</v>
       </c>
       <c r="R3" t="n">
-        <v>6396174.114388627</v>
+        <v>6396077</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +875,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I granplantering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,33 +894,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110636059</v>
+        <v>111534651</v>
       </c>
       <c r="B4" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,44 +924,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>Verkebäcksviken, Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595044.2781667351</v>
+        <v>595012</v>
       </c>
       <c r="R4" t="n">
-        <v>6396053.751719909</v>
+        <v>6395961</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -990,22 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,63 +1021,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110635405</v>
+        <v>112203732</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595102.8807649282</v>
+        <v>594803</v>
       </c>
       <c r="R5" t="n">
-        <v>6396067.427930923</v>
+        <v>6396141</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,22 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,33 +1111,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110636846</v>
+        <v>112236365</v>
       </c>
       <c r="B6" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,38 +1141,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dagsbo; Verkebäcksviken (Dagsbo; Verkebäcksviken), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594828.1389969039</v>
+        <v>594875</v>
       </c>
       <c r="R6" t="n">
-        <v>6396087.701019844</v>
+        <v>6396234</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,22 +1206,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,33 +1230,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110636824</v>
+        <v>112236222</v>
       </c>
       <c r="B7" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,38 +1260,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dagsbo; Verkebäcksviken (Dagsbo; Verkebäcksviken), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594821.877542478</v>
+        <v>594933</v>
       </c>
       <c r="R7" t="n">
-        <v>6396080.603669374</v>
+        <v>6396201</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,22 +1325,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,33 +1349,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110637170</v>
+        <v>121754592</v>
       </c>
       <c r="B8" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,44 +1379,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594776.452011085</v>
+        <v>595015</v>
       </c>
       <c r="R8" t="n">
-        <v>6396190.207268835</v>
+        <v>6396186</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1460,22 +1436,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,6 +1460,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1495,22 +1472,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111531519</v>
+        <v>110635067</v>
       </c>
       <c r="B9" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,43 +1490,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595038.3009655987</v>
+        <v>595126</v>
       </c>
       <c r="R9" t="n">
-        <v>6396057.353625069</v>
+        <v>6396073</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,22 +1554,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,51 +1596,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111534212</v>
+        <v>110636846</v>
       </c>
       <c r="B10" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dagsbo; Verkebäcksviken (Dagsbo; Verkebäcksviken), Sm</t>
+          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594805.9416275211</v>
+        <v>594828</v>
       </c>
       <c r="R10" t="n">
-        <v>6396074.883175282</v>
+        <v>6396088</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1691,22 +1662,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,37 +1694,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111537932</v>
+        <v>111538100</v>
       </c>
       <c r="B11" t="n">
-        <v>55602</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100070</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1771,10 +1727,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595043.4620112276</v>
+        <v>594974</v>
       </c>
       <c r="R11" t="n">
-        <v>6395974.603720695</v>
+        <v>6396224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,61 +1806,66 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand </t>
+          <t>Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111533937</v>
+        <v>111557447</v>
       </c>
       <c r="B12" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenhagen (Stenhagen), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594785.00034439</v>
+        <v>595124</v>
       </c>
       <c r="R12" t="n">
-        <v>6396145.498780883</v>
+        <v>6396086</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,19 +1892,14 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:23</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På samma tall!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,72 +1908,78 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111534111</v>
+        <v>112236205</v>
       </c>
       <c r="B13" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dagsbo; Verkebäcksviken (Dagsbo; Verkebäcksviken), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594805.9667103711</v>
+        <v>594931</v>
       </c>
       <c r="R13" t="n">
-        <v>6396073.814475322</v>
+        <v>6396214</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,22 +2003,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,33 +2027,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111538100</v>
+        <v>112236248</v>
       </c>
       <c r="B14" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2076,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2132,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594974.3931778221</v>
+        <v>594958</v>
       </c>
       <c r="R14" t="n">
-        <v>6396223.726530103</v>
+        <v>6396178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,22 +2122,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Två olika tallar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,54 +2163,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand </t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111538147</v>
+        <v>112203737</v>
       </c>
       <c r="B15" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>5448</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2253,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594796.7697831856</v>
+        <v>594803</v>
       </c>
       <c r="R15" t="n">
-        <v>6396123.320251373</v>
+        <v>6396141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2283,22 +2246,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,70 +2272,66 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand </t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111534059</v>
+        <v>112203709</v>
       </c>
       <c r="B16" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>5741</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenhagen (Stenhagen), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594794.6408354465</v>
+        <v>594781</v>
       </c>
       <c r="R16" t="n">
-        <v>6396122.73565076</v>
+        <v>6396169</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2406,22 +2355,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,81 +2369,78 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111533906</v>
+        <v>112204167</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenhagen (Stenhagen), Sm</t>
+          <t>A 30799, Storön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594786.359476931</v>
+        <v>594925</v>
       </c>
       <c r="R17" t="n">
-        <v>6396133.234054895</v>
+        <v>6396228</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2528,22 +2464,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2+7+1</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,33 +2483,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111534032</v>
+        <v>119535887</v>
       </c>
       <c r="B18" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,38 +2513,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenhagen (Stenhagen), Sm</t>
+          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594793.6954899583</v>
+        <v>594831</v>
       </c>
       <c r="R18" t="n">
-        <v>6396117.367083212</v>
+        <v>6396031</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2641,22 +2572,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,15 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111534246</v>
+        <v>121763950</v>
       </c>
       <c r="B19" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,44 +2625,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dagsbo; Verkebäcksviken (Dagsbo; Verkebäcksviken), Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594820.5764323578</v>
+        <v>594958</v>
       </c>
       <c r="R19" t="n">
-        <v>6396044.751846077</v>
+        <v>6396369</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2763,22 +2684,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,15 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111538210</v>
+        <v>121764658</v>
       </c>
       <c r="B20" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,45 +2737,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594797.6524209575</v>
+        <v>595027</v>
       </c>
       <c r="R20" t="n">
-        <v>6396131.360525105</v>
+        <v>6396283</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2883,22 +2796,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2907,82 +2820,75 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand </t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111533775</v>
+        <v>111537932</v>
       </c>
       <c r="B21" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>100070</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stenhagen (Stenhagen), Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594770.3573293557</v>
+        <v>595043</v>
       </c>
       <c r="R21" t="n">
-        <v>6396153.174710296</v>
+        <v>6395975</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3011,7 +2917,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3021,7 +2927,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3030,69 +2936,62 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111537976</v>
+        <v>111877566</v>
       </c>
       <c r="B22" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>53595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knölspindel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Araneus angulatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Clerck, 1757</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3100,13 +2999,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595117.0271231972</v>
+        <v>594855</v>
       </c>
       <c r="R22" t="n">
-        <v>6396058.137349035</v>
+        <v>6396225</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3133,19 +3032,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3166,70 +3055,59 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand </t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111531683</v>
+        <v>121753048</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595121.2346721888</v>
+        <v>594817</v>
       </c>
       <c r="R23" t="n">
-        <v>6396061.4443192</v>
+        <v>6396099</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3253,22 +3131,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,22 +3166,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111533687</v>
+        <v>121753875</v>
       </c>
       <c r="B24" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,47 +3184,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storön (Storön), Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594778.8316844747</v>
+        <v>594778</v>
       </c>
       <c r="R24" t="n">
-        <v>6396180.10514512</v>
+        <v>6396263</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3375,22 +3238,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,65 +3280,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111557317</v>
+        <v>111531519</v>
       </c>
       <c r="B25" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595102.7158081263</v>
+        <v>595038</v>
       </c>
       <c r="R25" t="n">
-        <v>6396028.929247913</v>
+        <v>6396057</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3502,82 +3354,66 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand </t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111557458</v>
+        <v>110635405</v>
       </c>
       <c r="B26" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3586,21 +3422,19 @@
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594776.3629612414</v>
+        <v>595103</v>
       </c>
       <c r="R26" t="n">
-        <v>6396125.514572047</v>
+        <v>6396067</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3624,22 +3458,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3648,61 +3482,55 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand </t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111557425</v>
+        <v>111531683</v>
       </c>
       <c r="B27" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3711,21 +3539,19 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595135.6715832634</v>
+        <v>595121</v>
       </c>
       <c r="R27" t="n">
-        <v>6396085.308774129</v>
+        <v>6396061</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3752,104 +3578,87 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand </t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111557447</v>
+        <v>111533906</v>
       </c>
       <c r="B28" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Stenhagen, Stenhagen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595123.8555299225</v>
+        <v>594786</v>
       </c>
       <c r="R28" t="n">
-        <v>6396086.634433704</v>
+        <v>6396134</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3876,60 +3685,39 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På samma tall!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand </t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111557388</v>
+        <v>111537976</v>
       </c>
       <c r="B29" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3956,7 +3744,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3973,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595120.4338386087</v>
+        <v>595117</v>
       </c>
       <c r="R29" t="n">
-        <v>6396027.207820597</v>
+        <v>6396058</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4018,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4039,22 +3827,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand </t>
+          <t>Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111557356</v>
+        <v>111557317</v>
       </c>
       <c r="B30" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4098,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595109.7638816066</v>
+        <v>595102</v>
       </c>
       <c r="R30" t="n">
-        <v>6396025.3526209</v>
+        <v>6396029</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4131,19 +3914,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4164,44 +3937,39 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand </t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111877566</v>
+        <v>111557356</v>
       </c>
       <c r="B31" t="n">
-        <v>52665</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100388</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knölspindel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Araneus angulatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Clerck, 1757</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4209,10 +3977,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4220,13 +3991,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594855</v>
+        <v>595109</v>
       </c>
       <c r="R31" t="n">
-        <v>6396225</v>
+        <v>6396025</v>
       </c>
       <c r="S31" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4276,71 +4047,67 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112204167</v>
+        <v>111557388</v>
       </c>
       <c r="B32" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 30799, Storön, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>594925</v>
+        <v>595121</v>
       </c>
       <c r="R32" t="n">
-        <v>6396228</v>
+        <v>6396027</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4364,17 +4131,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2+7+1</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4395,71 +4157,67 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112203732</v>
+        <v>112204281</v>
       </c>
       <c r="B33" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Samsvik, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>594803</v>
+        <v>595169</v>
       </c>
       <c r="R33" t="n">
-        <v>6396141</v>
+        <v>6396054</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4504,12 +4262,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4519,12 +4277,7 @@
         <v>112204297</v>
       </c>
       <c r="B34" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4631,15 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112204281</v>
+        <v>112204311</v>
       </c>
       <c r="B35" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4414,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4683,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595169</v>
+        <v>595113</v>
       </c>
       <c r="R35" t="n">
-        <v>6396054</v>
+        <v>6396025</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4746,50 +4494,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112203737</v>
+        <v>112236185</v>
       </c>
       <c r="B36" t="n">
-        <v>90896</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4797,13 +4541,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594803</v>
+        <v>594982</v>
       </c>
       <c r="R36" t="n">
-        <v>6396141</v>
+        <v>6396167</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4827,12 +4571,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4853,22 +4607,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112204311</v>
+        <v>112236282</v>
       </c>
       <c r="B37" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4895,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4908,17 +4657,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storön, Samsvik, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595112</v>
+        <v>594909</v>
       </c>
       <c r="R37" t="n">
-        <v>6396025</v>
+        <v>6396198</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4942,12 +4691,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4963,76 +4722,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112203709</v>
+        <v>119823610</v>
       </c>
       <c r="B38" t="n">
-        <v>89121</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5741</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Skitskär, Skitskär, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594781</v>
+        <v>595111</v>
       </c>
       <c r="R38" t="n">
-        <v>6396169</v>
+        <v>6396025</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5056,12 +4799,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5070,61 +4823,55 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112236468</v>
+        <v>121752765</v>
       </c>
       <c r="B39" t="n">
-        <v>103841</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5137,17 +4884,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594918</v>
+        <v>594837</v>
       </c>
       <c r="R39" t="n">
-        <v>6396098</v>
+        <v>6396023</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5171,22 +4918,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5202,76 +4949,72 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112237682</v>
+        <v>121754718</v>
       </c>
       <c r="B40" t="n">
-        <v>90376</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595194</v>
+        <v>594994</v>
       </c>
       <c r="R40" t="n">
-        <v>6396077</v>
+        <v>6396168</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,17 +5038,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>I granplantering</t>
+          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5321,27 +5074,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112236185</v>
+        <v>121754826</v>
       </c>
       <c r="B41" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5368,7 +5116,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5381,17 +5129,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594982</v>
+        <v>595008</v>
       </c>
       <c r="R41" t="n">
-        <v>6396167</v>
+        <v>6396135</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5415,22 +5163,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5446,77 +5194,64 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112236300</v>
+        <v>121763762</v>
       </c>
       <c r="B42" t="n">
-        <v>103841</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594877</v>
+        <v>594945</v>
       </c>
       <c r="R42" t="n">
-        <v>6396173</v>
+        <v>6396373</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5540,22 +5275,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5571,76 +5306,70 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112236205</v>
+        <v>110636059</v>
       </c>
       <c r="B43" t="n">
-        <v>89614</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594931</v>
+        <v>595044</v>
       </c>
       <c r="R43" t="n">
-        <v>6396214</v>
+        <v>6396053</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5664,22 +5393,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5688,34 +5407,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112236402</v>
+        <v>110636824</v>
       </c>
       <c r="B44" t="n">
-        <v>103841</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5740,32 +5453,21 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594889</v>
+        <v>594822</v>
       </c>
       <c r="R44" t="n">
-        <v>6396160</v>
+        <v>6396081</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5789,22 +5491,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5813,34 +5505,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112236222</v>
+        <v>110637139</v>
       </c>
       <c r="B45" t="n">
-        <v>89991</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5848,48 +5534,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Dagsbo, Dagsbo, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594933</v>
+        <v>594774</v>
       </c>
       <c r="R45" t="n">
-        <v>6396201</v>
+        <v>6396175</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5913,22 +5589,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5937,83 +5613,76 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112236248</v>
+        <v>110637170</v>
       </c>
       <c r="B46" t="n">
-        <v>89614</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594958</v>
+        <v>594777</v>
       </c>
       <c r="R46" t="n">
-        <v>6396178</v>
+        <v>6396190</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6037,27 +5706,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Två olika tallar.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6066,83 +5730,76 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112236365</v>
+        <v>111533687</v>
       </c>
       <c r="B47" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594875</v>
+        <v>594779</v>
       </c>
       <c r="R47" t="n">
-        <v>6396234</v>
+        <v>6396181</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6166,22 +5823,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6190,56 +5847,50 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112236282</v>
+        <v>111533775</v>
       </c>
       <c r="B48" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6253,21 +5904,19 @@
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Stenhagen, Stenhagen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>594909</v>
+        <v>594770</v>
       </c>
       <c r="R48" t="n">
-        <v>6396198</v>
+        <v>6396153</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6291,22 +5940,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6315,34 +5964,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112236343</v>
+        <v>111533937</v>
       </c>
       <c r="B49" t="n">
-        <v>103841</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6367,32 +6010,21 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Stenhagen, Stenhagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>594869</v>
+        <v>594785</v>
       </c>
       <c r="R49" t="n">
-        <v>6396235</v>
+        <v>6396145</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6416,22 +6048,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6440,83 +6072,67 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112236387</v>
+        <v>111534032</v>
       </c>
       <c r="B50" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1619</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>A 30779, Storön, Sm</t>
+          <t>Stenhagen, Stenhagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>594893</v>
+        <v>594794</v>
       </c>
       <c r="R50" t="n">
-        <v>6396172</v>
+        <v>6396118</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6540,27 +6156,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lågt på asp</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6569,77 +6180,76 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Greger Ström</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119535887</v>
+        <v>111534059</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
+          <t>Stenhagen, Stenhagen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594831</v>
+        <v>594795</v>
       </c>
       <c r="R51" t="n">
-        <v>6396031</v>
+        <v>6396122</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6663,22 +6273,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6705,50 +6315,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119823610</v>
+        <v>111534111</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skitskär, Skitskär, Sm</t>
+          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595111</v>
+        <v>594807</v>
       </c>
       <c r="R52" t="n">
-        <v>6396025</v>
+        <v>6396074</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6775,22 +6381,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6817,15 +6423,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121754357</v>
+        <v>111534212</v>
       </c>
       <c r="B53" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6851,16 +6452,17 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594927</v>
+        <v>594806</v>
       </c>
       <c r="R53" t="n">
-        <v>6396335</v>
+        <v>6396075</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6887,22 +6489,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6929,42 +6521,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121754718</v>
+        <v>111534246</v>
       </c>
       <c r="B54" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6973,21 +6560,19 @@
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Dagsbo; Verkebäcksviken, Dagsbo; Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594994</v>
+        <v>594821</v>
       </c>
       <c r="R54" t="n">
-        <v>6396168</v>
+        <v>6396045</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7011,27 +6596,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>300 knärötter återfunna. Underröjning har genomförts!  Hänsynssnitslar 2 meter ifrån.</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7040,7 +6610,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7052,22 +6621,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121753048</v>
+        <v>111538147</v>
       </c>
       <c r="B55" t="n">
-        <v>57744</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7075,41 +6639,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>594817</v>
+        <v>594797</v>
       </c>
       <c r="R55" t="n">
-        <v>6396099</v>
+        <v>6396123</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7133,22 +6701,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7157,33 +6725,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121752698</v>
+        <v>111538210</v>
       </c>
       <c r="B56" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7209,19 +6773,27 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594887</v>
+        <v>594798</v>
       </c>
       <c r="R56" t="n">
-        <v>6396036</v>
+        <v>6396131</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7245,22 +6817,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7269,33 +6841,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Louise Lundberg, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121753875</v>
+        <v>111557425</v>
       </c>
       <c r="B57" t="n">
-        <v>57744</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7303,37 +6871,49 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594778</v>
+        <v>595136</v>
       </c>
       <c r="R57" t="n">
-        <v>6396263</v>
+        <v>6396086</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7357,22 +6937,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7381,33 +6951,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121752859</v>
+        <v>111557458</v>
       </c>
       <c r="B58" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7434,7 +7000,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7447,17 +7013,17 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594807</v>
+        <v>594777</v>
       </c>
       <c r="R58" t="n">
-        <v>6396047</v>
+        <v>6396125</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7481,22 +7047,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:03</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7512,54 +7068,49 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Louise Lundberg, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121754826</v>
+        <v>112236300</v>
       </c>
       <c r="B59" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7572,17 +7123,17 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595008</v>
+        <v>594877</v>
       </c>
       <c r="R59" t="n">
-        <v>6396135</v>
+        <v>6396173</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7606,22 +7157,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7637,27 +7188,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121753035</v>
+        <v>112236343</v>
       </c>
       <c r="B60" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7682,20 +7228,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594815</v>
+        <v>594869</v>
       </c>
       <c r="R60" t="n">
-        <v>6396098</v>
+        <v>6396235</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7719,22 +7277,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7743,33 +7301,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121752813</v>
+        <v>112236402</v>
       </c>
       <c r="B61" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7804,19 +7358,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594841</v>
+        <v>594889</v>
       </c>
       <c r="R61" t="n">
-        <v>6396038</v>
+        <v>6396160</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7840,22 +7397,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7864,33 +7421,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121754592</v>
+        <v>112236468</v>
       </c>
       <c r="B62" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7898,40 +7451,49 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>A 30779, Storön, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595015</v>
+        <v>594918</v>
       </c>
       <c r="R62" t="n">
-        <v>6396186</v>
+        <v>6396098</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7955,22 +7517,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7986,74 +7548,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Greger Ström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121752765</v>
+        <v>121752698</v>
       </c>
       <c r="B63" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>594837</v>
+        <v>594887</v>
       </c>
       <c r="R63" t="n">
-        <v>6396023</v>
+        <v>6396036</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -8085,7 +7630,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8095,7 +7640,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8104,7 +7649,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8116,22 +7660,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121766306</v>
+        <v>121752813</v>
       </c>
       <c r="B64" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8156,14 +7695,23 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>594815</v>
+        <v>594841</v>
       </c>
       <c r="R64" t="n">
         <v>6396038</v>
@@ -8193,22 +7741,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8235,15 +7783,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121765794</v>
+        <v>121752859</v>
       </c>
       <c r="B65" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8268,20 +7811,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>594763</v>
+        <v>594807</v>
       </c>
       <c r="R65" t="n">
-        <v>6396128</v>
+        <v>6396047</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8305,22 +7860,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8329,6 +7884,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8340,65 +7896,55 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Louise Lundberg, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121764658</v>
+        <v>121753035</v>
       </c>
       <c r="B66" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>595027</v>
+        <v>594815</v>
       </c>
       <c r="R66" t="n">
-        <v>6396283</v>
+        <v>6396098</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8422,22 +7968,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8464,58 +8010,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121763950</v>
+        <v>121753453</v>
       </c>
       <c r="B67" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Dagsbo, Dagsbo, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>594958</v>
+        <v>594727</v>
       </c>
       <c r="R67" t="n">
-        <v>6396369</v>
+        <v>6396229</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8539,22 +8079,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8581,15 +8121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121764675</v>
+        <v>121754357</v>
       </c>
       <c r="B68" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8617,14 +8152,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storön, Storön, Sm</t>
+          <t>Rösundet, Rösundet, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>595041</v>
+        <v>594927</v>
       </c>
       <c r="R68" t="n">
-        <v>6396281</v>
+        <v>6396335</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8651,22 +8186,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8693,54 +8228,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121763762</v>
+        <v>121764675</v>
       </c>
       <c r="B69" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rösundet, Rösundet, Sm</t>
+          <t>Storön, Storön, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>594945</v>
+        <v>595041</v>
       </c>
       <c r="R69" t="n">
-        <v>6396373</v>
+        <v>6396281</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8772,7 +8298,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8782,7 +8308,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8791,7 +8317,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8813,12 +8338,7 @@
         <v>121765532</v>
       </c>
       <c r="B70" t="n">
-        <v>105264</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8919,6 +8439,220 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121765794</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>594763</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6396128</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121766306</v>
+      </c>
+      <c r="B72" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Storön A 30779-2023, Storön A 30779-2023, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>594815</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6396038</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
